--- a/generated/spreadsheet/hedgerow-removal-notice-hedgerow-removal.xlsx
+++ b/generated/spreadsheet/hedgerow-removal-notice-hedgerow-removal.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
@@ -568,14 +568,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -599,19 +599,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -630,19 +630,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -661,14 +661,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -732,13 +736,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -748,7 +752,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -767,23 +771,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -802,18 +806,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -837,23 +841,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -877,12 +885,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -892,7 +900,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -916,12 +924,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -931,7 +939,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -955,17 +963,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -984,22 +992,18 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1009,7 +1013,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1063,48 +1067,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1114,32 +1118,28 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1163,14 +1163,18 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1180,7 +1184,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1199,18 +1203,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1220,51 +1224,47 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1272,14 +1272,18 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1308,13 +1312,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1324,7 +1328,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1343,13 +1347,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1378,13 +1382,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1413,13 +1417,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1429,32 +1433,32 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1464,32 +1468,28 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1513,14 +1513,18 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1530,7 +1534,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1549,18 +1553,18 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1570,51 +1574,47 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1622,14 +1622,18 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1639,7 +1643,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1658,13 +1662,13 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1674,7 +1678,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1693,13 +1697,13 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1728,13 +1732,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1763,13 +1767,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1779,7 +1783,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1793,18 +1797,14 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1828,19 +1828,19 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1850,50 +1850,54 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Declaration</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1901,7 +1905,7 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1916,19 +1920,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1936,12 +1932,12 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1955,7 +1951,7 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1963,12 +1959,12 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1978,11 +1974,19 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Hedgerow removal notice</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Details of any hedgerows being removed as part of the development</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Removal reasons</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1990,7 +1994,7 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Reasons for the proposed removal of hedgerow(s)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2005,27 +2009,23 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Hedgerow removal notice</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Details of any hedgerows being removed as part of the development</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Removal reasons</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Reasons for the proposed removal of hedgerow(s)</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2044,24 +2044,20 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Hedgerow length</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Total length, in metres, of hedgerow proposed for removal</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2075,7 +2071,7 @@
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Hedgerow length</t>
+          <t>Hedgerow less than 30 years</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2083,12 +2079,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Total length, in metres, of hedgerow proposed for removal</t>
+          <t>Is the hedgerow less than 30 years old?</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2102,7 +2098,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Hedgerow less than 30 years</t>
+          <t>Planting evidence attached</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2110,7 +2106,7 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Is the hedgerow less than 30 years old?</t>
+          <t>Is evidence of the date of planting attached?</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2120,7 +2116,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2125,7 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Planting evidence attached</t>
+          <t>Interest declaration</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2137,26 +2133,34 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Is evidence of the date of planting attached?</t>
+          <t>The applicant's interest or ownership in the hedgerow</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Interest declaration</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2164,12 +2168,12 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>The applicant's interest or ownership in the hedgerow</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2179,19 +2183,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2199,17 +2195,17 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2214,7 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2226,7 +2222,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2245,7 +2241,7 @@
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2253,7 +2249,7 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2272,7 +2268,7 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2280,7 +2276,7 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2295,24 +2291,36 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2322,16 +2330,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -2339,19 +2339,19 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2370,14 +2370,14 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2401,19 +2401,19 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2463,14 +2463,14 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2525,19 +2525,19 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2556,14 +2556,14 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2578,50 +2578,46 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2629,12 +2625,12 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2648,7 +2644,7 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2656,17 +2652,17 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2675,15 +2671,19 @@
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2707,14 +2707,14 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -2738,14 +2738,14 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2754,37 +2754,6 @@
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -2792,28 +2761,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B57:B65"/>
-    <mergeCell ref="B66:B71"/>
-    <mergeCell ref="A34:A41"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B46:B51"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="A57:A65"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="B24:B29"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="B34:B41"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A42"/>
+    <mergeCell ref="A56:A64"/>
+    <mergeCell ref="B41"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A45:A50"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="A65:A70"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A33:A40"/>
+    <mergeCell ref="A41"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="B65:B70"/>
+    <mergeCell ref="B56:B64"/>
+    <mergeCell ref="B45:B50"/>
+    <mergeCell ref="B33:B40"/>
+    <mergeCell ref="A42:A44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/hedgerow-removal-notice-hedgerow-removal.xlsx
+++ b/generated/spreadsheet/hedgerow-removal-notice-hedgerow-removal.xlsx
@@ -1964,7 +1964,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">

--- a/generated/spreadsheet/hedgerow-removal-notice-hedgerow-removal.xlsx
+++ b/generated/spreadsheet/hedgerow-removal-notice-hedgerow-removal.xlsx
@@ -427,17 +427,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -491,29 +491,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -563,19 +563,19 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -594,24 +594,24 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -625,24 +625,24 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -656,28 +656,24 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -691,7 +687,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -701,13 +697,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -726,7 +722,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -736,13 +732,13 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -752,7 +748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -761,7 +757,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -771,23 +767,23 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -796,7 +792,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -806,18 +802,18 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -831,7 +827,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -841,27 +837,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -870,7 +862,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -900,7 +892,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -909,7 +901,7 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -924,12 +916,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -939,7 +931,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -948,7 +940,7 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -963,17 +955,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -987,33 +979,37 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1032,18 +1028,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1057,7 +1053,7 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1067,48 +1063,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1118,28 +1114,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1163,18 +1163,14 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1184,7 +1180,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1203,18 +1199,18 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1224,47 +1220,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1272,18 +1272,14 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1312,13 +1308,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1328,7 +1324,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1347,13 +1343,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1382,13 +1378,13 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1417,13 +1413,13 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1433,32 +1429,32 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1468,28 +1464,32 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1513,18 +1513,14 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1534,7 +1530,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1553,18 +1549,18 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1574,47 +1570,51 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1622,18 +1622,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1643,7 +1639,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1662,13 +1658,13 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1678,7 +1674,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1697,13 +1693,13 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1732,13 +1728,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1767,13 +1763,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1783,7 +1779,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1797,14 +1793,18 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1828,19 +1828,19 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -1850,54 +1850,50 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Declaration</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1905,7 +1901,7 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1920,11 +1916,19 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1932,12 +1936,12 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -1951,7 +1955,7 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1959,12 +1963,12 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1974,19 +1978,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Hedgerow removal notice</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Details of any hedgerows being removed as part of the development</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Removal reasons</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1994,12 +1990,12 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Reasons for the proposed removal of hedgerow(s)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2009,23 +2005,27 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Hedgerow removal notice</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Details of any hedgerows being removed as part of the development</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Removal reasons</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Reasons for the proposed removal of hedgerow(s)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2044,20 +2044,24 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Hedgerow length</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Total length, in metres, of hedgerow proposed for removal</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2071,7 +2075,7 @@
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Hedgerow less than 30 years</t>
+          <t>Hedgerow length</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2079,12 +2083,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Is the hedgerow less than 30 years old?</t>
+          <t>Total length, in metres, of hedgerow proposed for removal</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2098,7 +2102,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Planting evidence attached</t>
+          <t>Hedgerow less than 30 years</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2106,7 +2110,7 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Is evidence of the date of planting attached?</t>
+          <t>Is the hedgerow less than 30 years old?</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2116,7 +2120,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2129,7 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Interest declaration</t>
+          <t>Planting evidence attached</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2133,34 +2137,26 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The applicant's interest or ownership in the hedgerow</t>
+          <t>Is evidence of the date of planting attached?</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Interest declaration</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2168,12 +2164,12 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The applicant's interest or ownership in the hedgerow</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2183,11 +2179,19 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="2" t="n"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2195,17 +2199,17 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2218,7 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2222,7 +2226,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2241,7 +2245,7 @@
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2249,12 +2253,12 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2268,7 +2272,7 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2276,12 +2280,12 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2291,36 +2295,24 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2330,8 +2322,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="2" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -2339,19 +2339,19 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2370,14 +2370,14 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2401,19 +2401,19 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2432,19 +2432,19 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2463,19 +2463,19 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2525,19 +2525,19 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2556,14 +2556,14 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2578,46 +2578,50 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n"/>
-      <c r="B66" s="2" t="n"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2625,12 +2629,12 @@
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -2644,7 +2648,7 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2652,17 +2656,17 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2671,19 +2675,15 @@
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2707,14 +2707,14 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -2738,22 +2738,53 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -2761,28 +2792,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A56:A64"/>
-    <mergeCell ref="B41"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A45:A50"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="A65:A70"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="A33:A40"/>
-    <mergeCell ref="A41"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="B65:B70"/>
-    <mergeCell ref="B56:B64"/>
-    <mergeCell ref="B45:B50"/>
-    <mergeCell ref="B33:B40"/>
-    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B57:B65"/>
+    <mergeCell ref="B66:B71"/>
+    <mergeCell ref="A34:A41"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B46:B51"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="A57:A65"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B42"/>
+    <mergeCell ref="B24:B29"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="A42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/hedgerow-removal-notice-hedgerow-removal.xlsx
+++ b/generated/spreadsheet/hedgerow-removal-notice-hedgerow-removal.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -435,9 +435,9 @@
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1413,13 +1413,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1448,13 +1452,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1469,58 +1477,66 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Agent contact details</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Agent reference</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>A reference to an agent object</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1530,7 +1546,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1544,18 +1560,14 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1565,7 +1577,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1584,18 +1596,18 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1605,47 +1617,51 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information if an agent is being used.</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information if an agent is being used.</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>agent</t>
@@ -1653,18 +1669,14 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1674,7 +1686,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1693,13 +1705,13 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1709,7 +1721,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1728,13 +1740,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1763,13 +1775,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1798,13 +1810,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1814,7 +1830,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1828,14 +1844,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1859,19 +1883,27 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -1881,27 +1913,23 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -1911,51 +1939,55 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1963,12 +1995,12 @@
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -1978,11 +2010,19 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1990,12 +2030,12 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2005,19 +2045,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Hedgerow removal notice</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Details of any hedgerows being removed as part of the development</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Removal reasons</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2025,12 +2057,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Reasons for the proposed removal of hedgerow(s)</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2044,24 +2076,20 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2071,11 +2099,19 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Hedgerow removal notice</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Details of any hedgerows being removed as part of the development</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Hedgerow length</t>
+          <t>Removal reasons</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2083,12 +2119,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Total length, in metres, of hedgerow proposed for removal</t>
+          <t>Reasons for the proposed removal of hedgerow(s)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2102,20 +2138,24 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Hedgerow less than 30 years</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Is the hedgerow less than 30 years old?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2129,7 +2169,7 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Planting evidence attached</t>
+          <t>Hedgerow length</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2137,17 +2177,17 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Is evidence of the date of planting attached?</t>
+          <t>Total length, in metres, of hedgerow proposed for removal</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2196,7 @@
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Interest declaration</t>
+          <t>Hedgerow less than 30 years</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -2164,12 +2204,12 @@
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>The applicant's interest or ownership in the hedgerow</t>
+          <t>Is the hedgerow less than 30 years old?</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2179,19 +2219,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Planting evidence attached</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -2199,7 +2231,7 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Is evidence of the date of planting attached?</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2209,7 +2241,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2250,7 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Interest declaration</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -2226,26 +2258,34 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>The applicant's interest or ownership in the hedgerow</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="2" t="n"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2253,17 +2293,17 @@
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2312,7 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -2280,12 +2320,12 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2299,7 +2339,7 @@
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2307,7 +2347,7 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2322,36 +2362,24 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2365,19 +2393,15 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2392,8 +2416,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -2401,24 +2433,24 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2432,24 +2464,28 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2463,19 +2499,23 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -2494,19 +2534,23 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2525,19 +2569,23 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2556,19 +2604,19 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -2587,19 +2635,19 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -2609,37 +2657,33 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2648,34 +2692,46 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2683,17 +2739,17 @@
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2702,24 +2758,20 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -2733,19 +2785,15 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2755,7 +2803,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2769,22 +2817,84 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -2792,28 +2902,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B57:B65"/>
-    <mergeCell ref="B66:B71"/>
-    <mergeCell ref="A34:A41"/>
-    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="A48:A53"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B46:B51"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="A57:A65"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="A44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="B24:B30"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A35:A43"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="B24:B29"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="A59:A67"/>
+    <mergeCell ref="B68:B73"/>
+    <mergeCell ref="B59:B67"/>
+    <mergeCell ref="B35:B43"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="B44"/>
     <mergeCell ref="B20:B23"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A42"/>
+    <mergeCell ref="A68:A73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
